--- a/WorkLog_2026-08.xlsx
+++ b/WorkLog_2026-08.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sessions'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start Fixes'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'File Activity'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Punchlist Activity'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Punchlist Activity'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -77,13 +77,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1880,10 +1883,10 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -1892,7 +1895,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils_StartFix_20260819_142405.md; WorkLogGUI.py; start_fix.py</t>
+          <t>CRPUtils_StartFix_20260819_142405.md; start_fix.py</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2229,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2244,7 +2247,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>LoadSupplierWorkbooks</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
@@ -2255,33 +2258,33 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>WorkLog_2026-08.xlsx</t>
+          <t>oe_cleaning.py</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -2290,14 +2293,14 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>LoadSupplierWorkbooks</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -2306,7 +2309,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>oe_cleaning.py</t>
+          <t>PLM_CatalogRequestWorkbook.py; PLM_SupplierMOQProposal.py; PLM_VendorNameMismatch.py</t>
         </is>
       </c>
     </row>
@@ -2318,41 +2321,41 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>PLM_CatalogRequestWorkbook.py; PLM_SupplierMOQProposal.py; PLM_VendorNameMismatch.py</t>
+          <t>2026-08-21_06-55-14.snagx</t>
         </is>
       </c>
     </row>
@@ -2364,41 +2367,41 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>PycharmProjects</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>PLM</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Snagit</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>(root)</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H42" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.md, .py</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21_06-55-14.snagx</t>
+          <t>PLM_CatalogRequestQueue.py; PLM_CatalogRequest_EmailTemplates.md; PLM_Email.py; PLM_IngestPMCorrections.py; PLM_SendCatalogRequests.py</t>
         </is>
       </c>
     </row>
@@ -2410,20 +2413,20 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2432,10 +2435,10 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -2444,7 +2447,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>PLM_CatalogRequestQueue.py; PLM_CatalogRequest_EmailTemplates.md; PLM_Email.py; PLM_IngestPMCorrections.py; PLM_SendCatalogRequests.py</t>
+          <t>PLM-013_StartFix_20260821_084602.md; PLM-093_VendorFromDocuments_Design_draft.md; PLM_StockoutSourceOptions.py</t>
         </is>
       </c>
     </row>
@@ -2456,41 +2459,41 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>.md, .py</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>PLM-013_StartFix_20260821_084602.md; PLM-093_VendorFromDocuments_Design_draft.md; PLM_StockoutSourceOptions.py</t>
+          <t>AlternativeSupplierFinder.py; CRP_Vendor_Matcher.py; GlobalExhibitors_Rename_Migration.py; aapex_scraper_enhanced.py; aapex_to_excel.py</t>
         </is>
       </c>
     </row>
@@ -2502,41 +2505,41 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>AlternativeSupplierFinder.py; CRP_Vendor_Matcher.py; GlobalExhibitors_Rename_Migration.py; aapex_scraper_enhanced.py; aapex_to_excel.py</t>
+          <t>2026-08-21_10-22-32.snagx</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2551,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -2561,12 +2564,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
@@ -2577,12 +2580,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21_10-22-32.snagx</t>
+          <t>PLM_SendPMWorkbooks.py</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2597,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2612,7 +2615,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
@@ -2628,7 +2631,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>PLM_SendPMWorkbooks.py</t>
+          <t>automechanika_scraper.py</t>
         </is>
       </c>
     </row>
@@ -2640,16 +2643,16 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -2662,19 +2665,19 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.csv, .py</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>automechanika_scraper.py</t>
+          <t>am_promoted_suppliers.csv; promote_exhibitors_to_suppliers.py</t>
         </is>
       </c>
     </row>
@@ -2686,16 +2689,16 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2715,12 +2718,12 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>.csv, .py</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>am_promoted_suppliers.csv; promote_exhibitors_to_suppliers.py</t>
+          <t>VendorCapabilityClassifier.py; supplier_document_downloader.py</t>
         </is>
       </c>
     </row>
@@ -2732,16 +2735,16 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2754,19 +2757,15 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>.py</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>VendorCapabilityClassifier.py; supplier_document_downloader.py</t>
+          <t>.gitignore</t>
         </is>
       </c>
     </row>
@@ -2778,16 +2777,16 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2796,19 +2795,23 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>.html, .md</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>.gitignore</t>
+          <t>PLM_083_Partium_Feedback_draft.html; PLM_083_Partium_Feedback_draft.md</t>
         </is>
       </c>
     </row>
@@ -2820,16 +2823,16 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2838,40 +2841,40 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>LoadSupplierWorkbooks</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>.html, .md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>PLM_083_Partium_Feedback_draft.html; PLM_083_Partium_Feedback_draft.md</t>
+          <t>pdf_oe_extractor.py</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2884,7 +2887,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>LoadSupplierWorkbooks</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
@@ -2900,7 +2903,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>pdf_oe_extractor.py</t>
+          <t>VendorDocOEFit.py</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2915,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>00:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>00:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -2930,7 +2933,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -2946,24 +2949,24 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>VendorDocOEFit.py</t>
+          <t>PLM_NoSuggestionVendorMatch.py</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -2987,29 +2990,29 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>PLM_NoSuggestionVendorMatch.py</t>
+          <t>PLM-093_VendorOutreach_Email_draft.md</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -3022,7 +3025,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>LoadSupplierWorkbooks</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
@@ -3033,12 +3036,12 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.xml</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_VendorOutreach_Email_draft.md</t>
+          <t>pdoc_LoadSupplierWorkbooks.xml</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3053,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -3063,12 +3066,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>LoadSupplierWorkbooks</t>
+          <t>LOA-002</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
@@ -3079,12 +3082,12 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>.xml</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>pdoc_LoadSupplierWorkbooks.xml</t>
+          <t>LOA-002_StartFix_20260824_085304.md</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3099,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -3109,12 +3112,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>LOA-002</t>
+          <t>InternetDataImport</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
@@ -3125,12 +3128,12 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>LOA-002_StartFix_20260824_085304.md</t>
+          <t>LoadPartiumCompData.py</t>
         </is>
       </c>
     </row>
@@ -3142,16 +3145,16 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -3160,23 +3163,23 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>InternetDataImport</t>
+          <t>CRPUtils</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md, .xml</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>LoadPartiumCompData.py</t>
+          <t>CRP-014_StartFix_20260824_111354.md; pdoc_CRPUtils.xml</t>
         </is>
       </c>
     </row>
@@ -3188,16 +3191,16 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -3206,23 +3209,23 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>InternetDataImport</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>.md, .xml</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>CRP-014_StartFix_20260824_111354.md; pdoc_CRPUtils.xml</t>
+          <t>PartiumToScrapeRequest.py</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3237,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -3247,12 +3250,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>InternetDataImport</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
@@ -3263,12 +3266,12 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>PartiumToScrapeRequest.py</t>
+          <t>2026-08-24_12-03-51.snagx</t>
         </is>
       </c>
     </row>
@@ -3280,41 +3283,41 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>CRPUtils</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.md, .py</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24_12-03-51.snagx</t>
+          <t>CLAUDE.md; ro_data.py</t>
         </is>
       </c>
     </row>
@@ -3326,16 +3329,16 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -3344,23 +3347,23 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>BigDawgHunt</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>.md, .py</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md; ro_data.py</t>
+          <t>BDH_07_ScrapeRequestLoader.py</t>
         </is>
       </c>
     </row>
@@ -3372,12 +3375,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -3385,12 +3388,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>BigDawgHunt</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
@@ -3401,12 +3404,12 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>BDH_07_ScrapeRequestLoader.py</t>
+          <t>2026-08-24_14-51-02.snagx</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3421,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -3431,12 +3434,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -3447,12 +3450,12 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24_14-51-02.snagx</t>
+          <t>GLO-001_StartFix_20260824_160425.md</t>
         </is>
       </c>
     </row>
@@ -3464,16 +3467,16 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -3482,14 +3485,14 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -3498,7 +3501,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>GLO-001_StartFix_20260824_160425.md</t>
+          <t>PLM-093_NoSuggestion_VendorEmails_draft.md; PLM-094_StartFix_20260824_163035.md</t>
         </is>
       </c>
     </row>
@@ -3510,41 +3513,41 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_NoSuggestion_VendorEmails_draft.md; PLM-094_StartFix_20260824_163035.md</t>
+          <t>2026-08-24_17-27-11.snagx</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3559,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
@@ -3569,12 +3572,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
@@ -3585,29 +3588,29 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24_17-27-11.snagx</t>
+          <t>PLM_NoSuggestionOutlookDrafts.py</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
@@ -3615,12 +3618,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
@@ -3631,12 +3634,12 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>PLM_NoSuggestionOutlookDrafts.py</t>
+          <t>2026-08-25_06-08-26.snagx</t>
         </is>
       </c>
     </row>
@@ -3648,41 +3651,41 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.md, .py</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25_06-08-26.snagx</t>
+          <t>PLM-093_Workbook_Reconciliation_Note.md; erp_vendor_xref.py</t>
         </is>
       </c>
     </row>
@@ -3694,16 +3697,16 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -3723,12 +3726,12 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>.md, .py</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_Workbook_Reconciliation_Note.md; erp_vendor_xref.py</t>
+          <t>PLM_VendorCatalogOverlap.py; vendor_usness.py</t>
         </is>
       </c>
     </row>
@@ -3740,12 +3743,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
@@ -3774,7 +3777,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>PLM_VendorCatalogOverlap.py; vendor_usness.py</t>
+          <t>PLM_NoSuggestionCapabilityMatch.py; PLM_VendorOutreach.py</t>
         </is>
       </c>
     </row>
@@ -3786,25 +3789,25 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
@@ -3815,12 +3818,12 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md, .snagx</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>PLM_NoSuggestionCapabilityMatch.py; PLM_VendorOutreach.py</t>
+          <t>2026-08-25_11-55-15.snagx; CLAUDE.md</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3835,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3841,32 +3844,32 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>CRPUtils</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>.md, .snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25_11-55-15.snagx; CLAUDE.md</t>
+          <t>excel_format.py</t>
         </is>
       </c>
     </row>
@@ -3878,16 +3881,16 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3896,23 +3899,23 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md, .py</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>excel_format.py</t>
+          <t>PLM-093_PMA_COO_Email_draft.md; PLM-094_SmellTest_PLM093_Audit_20260824.md; PLM_080_NoSuggestionExport.py; PLM_093_ExecWorkbook.py; PLM_CategoryWorkbook.py</t>
         </is>
       </c>
     </row>
@@ -3924,16 +3927,16 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3946,10 +3949,10 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
@@ -3958,7 +3961,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_PMA_COO_Email_draft.md; PLM-094_SmellTest_PLM093_Audit_20260824.md; PLM_080_NoSuggestionExport.py; PLM_093_ExecWorkbook.py; PLM_CategoryWorkbook.py</t>
+          <t>GLO-002_Handoff_from_PLM.md; PLM_CategoryDigest.py</t>
         </is>
       </c>
     </row>
@@ -3970,16 +3973,16 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3988,7 +3991,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
@@ -3999,12 +4002,12 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>.md, .py</t>
+          <t>.md, .xml</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>GLO-002_Handoff_from_PLM.md; PLM_CategoryDigest.py</t>
+          <t>GLO-002_StartFix_20260825_182839.md; pdoc_GlobalSuppliers.xml</t>
         </is>
       </c>
     </row>
@@ -4016,58 +4019,58 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>.md, .xml</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>GLO-002_StartFix_20260825_182839.md; pdoc_GlobalSuppliers.xml</t>
+          <t>2026-08-25_19-26-47.snagx</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
@@ -4075,12 +4078,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
@@ -4091,12 +4094,12 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25_19-26-47.snagx</t>
+          <t>PLM-095_StartFix_20260826_081708.md</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4111,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -4121,7 +4124,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4130,19 +4133,19 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.docx, .md</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>PLM-095_StartFix_20260826_081708.md</t>
+          <t>PLM-092_AutoEyes_Severity_Reconciliation_scope.md; PLM-095_FillRateDiagnostic_MeetingBrief_20260826.docx; PLM-095_FillRateDiagnostic_MeetingBrief_20260826.md</t>
         </is>
       </c>
     </row>
@@ -4154,16 +4157,16 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -4188,7 +4191,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>PLM-092_AutoEyes_Severity_Reconciliation_scope.md; PLM-095_FillRateDiagnostic_MeetingBrief_20260826.docx; PLM-095_FillRateDiagnostic_MeetingBrief_20260826.md</t>
+          <t>20260826_Fill Rate Improvement Initiatives Update 8.26.26.docx; PLM_Review_ScottFillRateInitiatives_20260826.md; PLM_VendorReliabilityTier_Bug_20260826.md</t>
         </is>
       </c>
     </row>
@@ -4200,20 +4203,20 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4222,44 +4225,44 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>.docx, .md</t>
+          <t>.md, .py</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>20260826_Fill Rate Improvement Initiatives Update 8.26.26.docx; PLM_Review_ScottFillRateInitiatives_20260826.md; PLM_VendorReliabilityTier_Bug_20260826.md</t>
+          <t>PLM-081_StartFix_20260826_125342.md; PLM_ConsistencyLedger.py</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4268,40 +4271,40 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>.md, .py</t>
+          <t>.md, .py, .xml</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>PLM-081_StartFix_20260826_125342.md; PLM_ConsistencyLedger.py</t>
+          <t>PLM-081_CrossSurfaceConsistency_proposal_20260826.md; PLM-092_StartFix_20260827_054917.md; PLM-096_StartFix_20260827_054030.md; PLM_Orchestrator.py; PLM_SmellTest.py</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -4314,19 +4317,19 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>.md, .py, .xml</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>PLM-081_CrossSurfaceConsistency_proposal_20260826.md; PLM-092_StartFix_20260827_054917.md; PLM-096_StartFix_20260827_054030.md; PLM_Orchestrator.py; PLM_SmellTest.py</t>
+          <t>PLM_AutoEyes.py; PLM_FindingDefinition.py</t>
         </is>
       </c>
     </row>
@@ -4338,16 +4341,16 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -4360,36 +4363,36 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>PLM_AutoEyes.py; PLM_FindingDefinition.py</t>
+          <t>PLM_FindingSeverity_Ownership_20260828.md</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
@@ -4397,12 +4400,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
@@ -4413,12 +4416,12 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>PLM_FindingSeverity_Ownership_20260828.md</t>
+          <t>2026-08-30_13-31-46.snagx</t>
         </is>
       </c>
     </row>
@@ -4430,12 +4433,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
@@ -4443,12 +4446,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
@@ -4459,29 +4462,29 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30_13-31-46.snagx</t>
+          <t>promote_existing_vendor_oes_to_suppliers.py</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
@@ -4494,7 +4497,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>BigDawgHunt</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
@@ -4505,12 +4508,12 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>promote_existing_vendor_oes_to_suppliers.py</t>
+          <t>DeadDawg.xlsx</t>
         </is>
       </c>
     </row>
@@ -4522,16 +4525,16 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -4540,23 +4543,23 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>BigDawgHunt</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.md, .xlsx</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>DeadDawg.xlsx</t>
+          <t>Deep dive HPS file for Scott 8-1-26.xlsx; PLM_HPS_vs_EarlyWarning_Comparison_20260828.md</t>
         </is>
       </c>
     </row>
@@ -4568,41 +4571,41 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>.md, .xlsx</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Deep dive HPS file for Scott 8-1-26.xlsx; PLM_HPS_vs_EarlyWarning_Comparison_20260828.md</t>
+          <t>2026-08-31_15-54-00.snagx</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4617,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
@@ -4632,7 +4635,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>ebayBrowse</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
@@ -4643,102 +4646,10 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>.sql</t>
+          <t>.txt</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>ro_query.sql</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Snagit</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>(root)</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>.snagx</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31_15-54-00.snagx</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>PycharmProjects</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>ebayBrowse</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>.txt</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>token_file.txt</t>
         </is>
@@ -5173,7 +5084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6534,7 +6445,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46253.62070729861</v>
+        <v>46253.62070734492</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
@@ -6548,7 +6459,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>WorkLogGUI.py</t>
+          <t>start_fix.py</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -6557,40 +6468,40 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>25.1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46253.62070734492</v>
+        <v>46254.57084175104</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>start_fix.py</t>
+          <t>2026-08-20_13-42-00.snagx</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>57</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46254.57084175104</v>
+        <v>46254.59106476397</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
@@ -6604,7 +6515,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20_13-42-00.snagx</t>
+          <t>2026-08-20_14-10-45.snagx</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6613,12 +6524,12 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>77.5</v>
+        <v>298.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46254.59106476397</v>
+        <v>46254.59392497381</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
@@ -6632,7 +6543,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20_14-10-45.snagx</t>
+          <t>2026-08-20_14-15-14.snagx</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6641,96 +6552,96 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>298.7</v>
+        <v>461.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46254.59392497381</v>
+        <v>46254.6061574074</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20_14-15-14.snagx</t>
+          <t>GlobalSuppliers_dump_20260820.xlsx</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>461.2</v>
+        <v>2317.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46254.6061574074</v>
+        <v>46254.62835648148</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers_dump_20260820.xlsx</t>
+          <t>PLM-093_StartFix_20260820_150450.md</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>2317.6</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46254.62835648148</v>
+        <v>46254.6998830408</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_StartFix_20260820_150450.md</t>
+          <t>2026-08-20_16-47-49.snagx</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>145.7</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46254.6998830408</v>
+        <v>46254.70010646912</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
@@ -6744,7 +6655,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20_16-47-49.snagx</t>
+          <t>2026-08-20_16-48-09.snagx</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6753,96 +6664,96 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46254.70010646912</v>
+        <v>46254.71237262784</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20_16-48-09.snagx</t>
+          <t>PLM_083_PartiumResultsFilter.py</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>102.3</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46254.71237262784</v>
+        <v>46254.74004240439</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>PLM_083_PartiumResultsFilter.py</t>
+          <t>2026-08-20_17-45-39.snagx</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>10.6</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46254.74004240439</v>
+        <v>46254.81458997871</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>LoadSupplierWorkbooks</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20_17-45-39.snagx</t>
+          <t>oe_cleaning.py</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>248.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46254.75405730453</v>
+        <v>46255.25274119814</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
@@ -6851,26 +6762,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>WorkLog_2026-08.xlsx</t>
+          <t>PLM_VendorNameMismatch.py</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>16</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46254.81458997871</v>
+        <v>46255.25995379606</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
@@ -6879,12 +6790,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>LoadSupplierWorkbooks</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>oe_cleaning.py</t>
+          <t>PLM_CatalogRequestWorkbook.py</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -6893,12 +6804,12 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>2.4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46255.25274119814</v>
+        <v>46255.26296101037</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
@@ -6912,7 +6823,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>PLM_VendorNameMismatch.py</t>
+          <t>PLM_SupplierMOQProposal.py</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -6921,40 +6832,40 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46255.25995379606</v>
+        <v>46255.28836646735</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>PLM_CatalogRequestWorkbook.py</t>
+          <t>2026-08-21_06-55-14.snagx</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>15</v>
+        <v>293.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46255.26296101037</v>
+        <v>46255.29249435436</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
@@ -6968,7 +6879,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>PLM_SupplierMOQProposal.py</t>
+          <t>PLM_Email.py</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6977,40 +6888,40 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>21.1</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46255.28836646735</v>
+        <v>46255.30127733493</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21_06-55-14.snagx</t>
+          <t>PLM_IngestPMCorrections.py</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>293.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46255.29249435436</v>
+        <v>46255.30291200135</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
@@ -7024,7 +6935,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>PLM_Email.py</t>
+          <t>PLM_SendCatalogRequests.py</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7033,12 +6944,12 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46255.30127733493</v>
+        <v>46255.30442461401</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
@@ -7052,7 +6963,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>PLM_IngestPMCorrections.py</t>
+          <t>PLM_CatalogRequestQueue.py</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -7061,12 +6972,12 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>8.4</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46255.30291200135</v>
+        <v>46255.31464042365</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
@@ -7080,25 +6991,25 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>PLM_SendCatalogRequests.py</t>
+          <t>PLM_CatalogRequest_EmailTemplates.md</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46255.30442461401</v>
+        <v>46255.36530092593</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -7108,21 +7019,21 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>PLM_CatalogRequestQueue.py</t>
+          <t>PLM-013_StartFix_20260821_084602.md</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>18.3</v>
+        <v>154.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46255.31464042365</v>
+        <v>46255.3831197355</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
@@ -7136,49 +7047,49 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>PLM_CatalogRequest_EmailTemplates.md</t>
+          <t>PLM_StockoutSourceOptions.py</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>3.6</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46255.36530092593</v>
+        <v>46255.38704484989</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>PLM-013_StartFix_20260821_084602.md</t>
+          <t>aapex_scraper_enhanced.py</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>154.3</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46255.3831197355</v>
+        <v>46255.3870941491</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
@@ -7187,12 +7098,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PLM_StockoutSourceOptions.py</t>
+          <t>AlternativeSupplierFinder.py</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -7201,12 +7112,12 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46255.38704484989</v>
+        <v>46255.38716398217</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
@@ -7220,7 +7131,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>aapex_scraper_enhanced.py</t>
+          <t>aapex_to_excel.py</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -7229,12 +7140,12 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>20.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46255.3870941491</v>
+        <v>46255.38724379094</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
@@ -7248,7 +7159,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>AlternativeSupplierFinder.py</t>
+          <t>CRP_Vendor_Matcher.py</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -7257,12 +7168,12 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>19.6</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46255.38716398217</v>
+        <v>46255.38851576208</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
@@ -7276,7 +7187,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>aapex_to_excel.py</t>
+          <t>GlobalExhibitors_Rename_Migration.py</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -7285,12 +7196,12 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46255.38724379094</v>
+        <v>46255.39065409102</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
@@ -7299,54 +7210,54 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CRP_Vendor_Matcher.py</t>
+          <t>PLM-093_VendorFromDocuments_Design_draft.md</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>17.1</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46255.38851576208</v>
+        <v>46255.43231705131</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>GlobalExhibitors_Rename_Migration.py</t>
+          <t>2026-08-21_10-22-32.snagx</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>5.9</v>
+        <v>162.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46255.39065409102</v>
+        <v>46255.43490040422</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
@@ -7360,49 +7271,49 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_VendorFromDocuments_Design_draft.md</t>
+          <t>PLM_SendPMWorkbooks.py</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>19.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46255.43231705131</v>
+        <v>46255.44167348099</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21_10-22-32.snagx</t>
+          <t>automechanika_scraper.py</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>162.6</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46255.43490040422</v>
+        <v>46255.46252577005</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
@@ -7411,12 +7322,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>PLM_SendPMWorkbooks.py</t>
+          <t>promote_exhibitors_to_suppliers.py</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7425,12 +7336,12 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46255.44167348099</v>
+        <v>46255.47215501245</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
@@ -7444,21 +7355,21 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>automechanika_scraper.py</t>
+          <t>am_promoted_suppliers.csv</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>13.9</v>
+        <v>332.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46255.46252577005</v>
+        <v>46255.67940131521</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
@@ -7472,7 +7383,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>promote_exhibitors_to_suppliers.py</t>
+          <t>supplier_document_downloader.py</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7481,12 +7392,12 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>9.1</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46255.47215501245</v>
+        <v>46255.68981392631</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
@@ -7500,21 +7411,21 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>am_promoted_suppliers.csv</t>
+          <t>VendorCapabilityClassifier.py</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>332.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46255.67940131521</v>
+        <v>46255.79469040097</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
@@ -7528,21 +7439,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>supplier_document_downloader.py</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>.py</t>
-        </is>
-      </c>
+          <t>.gitignore</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="n">
-        <v>20.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46255.68981392631</v>
+        <v>46255.84154186956</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
@@ -7551,26 +7458,26 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>VendorCapabilityClassifier.py</t>
+          <t>PLM_083_Partium_Feedback_draft.html</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.html</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>12.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46255.79469040097</v>
+        <v>46255.84159691918</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
@@ -7579,22 +7486,26 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>.gitignore</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
+          <t>PLM_083_Partium_Feedback_draft.md</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>.md</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46255.84154186956</v>
+        <v>46255.97209698395</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
@@ -7603,26 +7514,26 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>LoadSupplierWorkbooks</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>PLM_083_Partium_Feedback_draft.html</t>
+          <t>pdf_oe_extractor.py</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>.html</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46255.84159691918</v>
+        <v>46256.02174596486</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
@@ -7631,26 +7542,26 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>PLM_083_Partium_Feedback_draft.md</t>
+          <t>VendorDocOEFit.py</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>6.3</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46255.97209698395</v>
+        <v>46256.37577764737</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
@@ -7659,12 +7570,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>LoadSupplierWorkbooks</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>pdf_oe_extractor.py</t>
+          <t>PLM_NoSuggestionVendorMatch.py</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7673,12 +7584,12 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>6.5</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46256.02174596486</v>
+        <v>46257.75100637153</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
@@ -7687,26 +7598,26 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>VendorDocOEFit.py</t>
+          <t>PLM-093_VendorOutreach_Email_draft.md</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>21.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46256.37577764737</v>
+        <v>46258.37005745184</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
@@ -7715,40 +7626,40 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>LoadSupplierWorkbooks</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>PLM_NoSuggestionVendorMatch.py</t>
+          <t>pdoc_LoadSupplierWorkbooks.xml</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.xml</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>13.1</v>
+        <v>235.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46257.75100637153</v>
+        <v>46258.37018518519</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>LOA-002</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_VendorOutreach_Email_draft.md</t>
+          <t>LOA-002_StartFix_20260824_085304.md</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7757,12 +7668,12 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46258.37005745184</v>
+        <v>46258.44347416551</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
@@ -7771,73 +7682,73 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>LoadSupplierWorkbooks</t>
+          <t>InternetDataImport</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>pdoc_LoadSupplierWorkbooks.xml</t>
+          <t>LoadPartiumCompData.py</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>.xml</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>235.4</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46258.37018518519</v>
+        <v>46258.46775123795</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>LOA-002</t>
+          <t>CRPUtils</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LOA-002_StartFix_20260824_085304.md</t>
+          <t>pdoc_CRPUtils.xml</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.xml</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>5.6</v>
+        <v>1019.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258.44347416551</v>
+        <v>46258.46798611111</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>InternetDataImport</t>
+          <t>CRPUtils</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>LoadPartiumCompData.py</t>
+          <t>CRP-014_StartFix_20260824_111354.md</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
@@ -7846,7 +7757,7 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46258.46775123795</v>
+        <v>46258.49030119524</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
@@ -7855,54 +7766,54 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>InternetDataImport</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>pdoc_CRPUtils.xml</t>
+          <t>PartiumToScrapeRequest.py</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>.xml</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>1019.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46258.46798611111</v>
+        <v>46258.50267592954</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>CRP-014_StartFix_20260824_111354.md</t>
+          <t>2026-08-24_12-03-51.snagx</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>15.3</v>
+        <v>119.8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46258.49030119524</v>
+        <v>46258.54789208598</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
@@ -7911,54 +7822,54 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>InternetDataImport</t>
+          <t>CRPUtils</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>PartiumToScrapeRequest.py</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46258.50267592954</v>
+        <v>46258.54789212067</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>CRPUtils</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24_12-03-51.snagx</t>
+          <t>ro_data.py</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>119.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46258.54789208598</v>
+        <v>46258.61515661835</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
@@ -7967,124 +7878,124 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>BigDawgHunt</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>BDH_07_ScrapeRequestLoader.py</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.8</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46258.54789212067</v>
+        <v>46258.61938461816</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>ro_data.py</t>
+          <t>2026-08-24_14-51-02.snagx</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>5.1</v>
+        <v>455.2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46258.61515661835</v>
+        <v>46258.6697337963</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>BigDawgHunt</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>BDH_07_ScrapeRequestLoader.py</t>
+          <t>GLO-001_StartFix_20260824_160425.md</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>37.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46258.61938461816</v>
+        <v>46258.68790509259</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24_14-51-02.snagx</t>
+          <t>PLM-094_StartFix_20260824_163035.md</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>455.2</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46258.6697337963</v>
+        <v>46258.68815997217</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>GLO-001_StartFix_20260824_160425.md</t>
+          <t>PLM-093_NoSuggestion_VendorEmails_draft.md</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -8093,40 +8004,40 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46258.68790509259</v>
+        <v>46258.72721771966</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>PLM-094_StartFix_20260824_163035.md</t>
+          <t>2026-08-24_17-27-11.snagx</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>152.8</v>
+        <v>164.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46258.68815997217</v>
+        <v>46258.73331958499</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
@@ -8140,21 +8051,21 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_NoSuggestion_VendorEmails_draft.md</t>
+          <t>PLM_NoSuggestionOutlookDrafts.py</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>5.8</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46258.72721771966</v>
+        <v>46259.25586518464</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
@@ -8168,7 +8079,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24_17-27-11.snagx</t>
+          <t>2026-08-25_06-08-26.snagx</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -8177,12 +8088,12 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>164.6</v>
+        <v>500.8</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46258.73331958499</v>
+        <v>46259.39697514119</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
@@ -8196,49 +8107,49 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>PLM_NoSuggestionOutlookDrafts.py</t>
+          <t>PLM-093_Workbook_Reconciliation_Note.md</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>13.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46259.25586518464</v>
+        <v>46259.40130494406</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25_06-08-26.snagx</t>
+          <t>erp_vendor_xref.py</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>500.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46259.39697514119</v>
+        <v>46259.43779507176</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
@@ -8252,21 +8163,21 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_Workbook_Reconciliation_Note.md</t>
+          <t>vendor_usness.py</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46259.40130494406</v>
+        <v>46259.43800008582</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
@@ -8280,7 +8191,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>erp_vendor_xref.py</t>
+          <t>PLM_VendorCatalogOverlap.py</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -8289,12 +8200,12 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>5.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46259.43779507176</v>
+        <v>46259.48910687343</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
@@ -8308,7 +8219,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>vendor_usness.py</t>
+          <t>PLM_NoSuggestionCapabilityMatch.py</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -8317,12 +8228,12 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46259.43800008582</v>
+        <v>46259.48925589228</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
@@ -8336,7 +8247,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>PLM_VendorCatalogOverlap.py</t>
+          <t>PLM_VendorOutreach.py</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -8345,40 +8256,40 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46259.48910687343</v>
+        <v>46259.49670295051</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>PLM_NoSuggestionCapabilityMatch.py</t>
+          <t>2026-08-25_11-55-15.snagx</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>191.9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46259.48925589228</v>
+        <v>46259.4996190966</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
@@ -8387,12 +8298,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>CRPUtils</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>PLM_VendorOutreach.py</t>
+          <t>excel_format.py</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -8401,16 +8312,16 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>10.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46259.49670295051</v>
+        <v>46259.49987254419</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8420,21 +8331,21 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25_11-55-15.snagx</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>191.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46259.4996190966</v>
+        <v>46259.70064070974</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
@@ -8443,26 +8354,26 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>CRPUtils</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>excel_format.py</t>
+          <t>PLM-094_SmellTest_PLM093_Audit_20260824.md</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46259.49987254419</v>
+        <v>46259.70129214902</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
@@ -8471,26 +8382,26 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>PLM_CategoryWorkbook.py</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46259.70064070974</v>
+        <v>46259.70316345814</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
@@ -8504,21 +8415,21 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>PLM-094_SmellTest_PLM093_Audit_20260824.md</t>
+          <t>PLM_080_NoSuggestionExport.py</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>11.4</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46259.70129214902</v>
+        <v>46259.70316348127</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
@@ -8532,7 +8443,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>PLM_CategoryWorkbook.py</t>
+          <t>PLM_UnreliableVendorAltMatch.py</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -8541,12 +8452,12 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46259.70316345814</v>
+        <v>46259.71396317094</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
@@ -8560,7 +8471,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>PLM_080_NoSuggestionExport.py</t>
+          <t>PLM_093_ExecWorkbook.py</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8569,12 +8480,12 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>36.3</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46259.70316348127</v>
+        <v>46259.71894312654</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
@@ -8588,21 +8499,21 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>PLM_UnreliableVendorAltMatch.py</t>
+          <t>PLM-093_PMA_COO_Email_draft.md</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46259.71396317094</v>
+        <v>46259.7691730786</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
@@ -8616,7 +8527,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>PLM_093_ExecWorkbook.py</t>
+          <t>PLM_CategoryDigest.py</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -8625,12 +8536,12 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>18.9</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46259.71894312654</v>
+        <v>46259.76964634768</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
@@ -8639,54 +8550,54 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>PLM-093_PMA_COO_Email_draft.md</t>
+          <t>pdoc_GlobalSuppliers.xml</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.xml</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>5.5</v>
+        <v>641.7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46259.7691730786</v>
+        <v>46259.76989583333</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>PLM_CategoryDigest.py</t>
+          <t>GLO-002_StartFix_20260825_182839.md</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>26.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46259.76964634768</v>
+        <v>46259.77627568453</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
@@ -8695,58 +8606,58 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>pdoc_GlobalSuppliers.xml</t>
+          <t>GLO-002_Handoff_from_PLM.md</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>.xml</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>641.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46259.76989583333</v>
+        <v>46259.81027835527</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>GLO-002_StartFix_20260825_182839.md</t>
+          <t>2026-08-25_19-26-47.snagx</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>13.9</v>
+        <v>461.3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46259.77627568453</v>
+        <v>46260.34523148148</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -8756,7 +8667,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>GLO-002_Handoff_from_PLM.md</t>
+          <t>PLM-095_StartFix_20260826_081708.md</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -8765,44 +8676,44 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>3.2</v>
+        <v>159.3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46259.81027835527</v>
+        <v>46260.44792387051</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25_19-26-47.snagx</t>
+          <t>PLM-095_FillRateDiagnostic_MeetingBrief_20260826.md</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>461.3</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46260.34523148148</v>
+        <v>46260.44933243992</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -8812,7 +8723,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>PLM-095_StartFix_20260826_081708.md</t>
+          <t>PLM-092_AutoEyes_Severity_Reconciliation_scope.md</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -8821,12 +8732,12 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>159.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46260.44792387051</v>
+        <v>46260.45199153818</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
@@ -8840,21 +8751,21 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>PLM-095_FillRateDiagnostic_MeetingBrief_20260826.md</t>
+          <t>PLM-095_FillRateDiagnostic_MeetingBrief_20260826.docx</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.docx</t>
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>12.4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46260.44933243992</v>
+        <v>46260.49273262887</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
@@ -8868,21 +8779,21 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>PLM-092_AutoEyes_Severity_Reconciliation_scope.md</t>
+          <t>20260826_Fill Rate Improvement Initiatives Update 8.26.26.docx</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.docx</t>
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>5</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46260.45199153818</v>
+        <v>46260.49700615799</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
@@ -8896,21 +8807,21 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>PLM-095_FillRateDiagnostic_MeetingBrief_20260826.docx</t>
+          <t>PLM_Review_ScottFillRateInitiatives_20260826.md</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>.docx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>43</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46260.49273262887</v>
+        <v>46260.49729301571</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
@@ -8924,25 +8835,25 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>20260826_Fill Rate Improvement Initiatives Update 8.26.26.docx</t>
+          <t>PLM_VendorReliabilityTier_Bug_20260826.md</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>.docx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>22.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46260.49700615799</v>
+        <v>46260.53729166667</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -8952,7 +8863,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>PLM_Review_ScottFillRateInitiatives_20260826.md</t>
+          <t>PLM-081_StartFix_20260826_125342.md</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -8961,12 +8872,12 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>7.9</v>
+        <v>163.9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46260.49729301571</v>
+        <v>46260.55493062991</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
@@ -8980,25 +8891,25 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>PLM_VendorReliabilityTier_Bug_20260826.md</t>
+          <t>PLM_ConsistencyLedger.py</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>3.5</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46260.53729166667</v>
+        <v>46261.21788664779</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -9008,21 +8919,21 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>PLM-081_StartFix_20260826_125342.md</t>
+          <t>PLM_SmellTest.py</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>163.9</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46260.55493062991</v>
+        <v>46261.21803733069</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
@@ -9036,7 +8947,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>PLM_ConsistencyLedger.py</t>
+          <t>PLM_Orchestrator.py</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -9045,12 +8956,12 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>35.4</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46261.21788664779</v>
+        <v>46261.22666671762</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
@@ -9064,25 +8975,25 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>PLM_SmellTest.py</t>
+          <t>PLM-081_CrossSurfaceConsistency_proposal_20260826.md</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>84.59999999999999</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46261.21803733069</v>
+        <v>46261.23645833333</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>StartFix</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -9092,21 +9003,21 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>PLM_Orchestrator.py</t>
+          <t>PLM-096_StartFix_20260827_054030.md</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>75.5</v>
+        <v>166.1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46261.22666671762</v>
+        <v>46261.23945318328</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
@@ -9120,21 +9031,21 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>PLM-081_CrossSurfaceConsistency_proposal_20260826.md</t>
+          <t>PLM_VendorReliability.py</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>4.8</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46261.23645833333</v>
+        <v>46261.24255787037</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
@@ -9148,7 +9059,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>PLM-096_StartFix_20260827_054030.md</t>
+          <t>PLM-092_StartFix_20260827_054917.md</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9157,12 +9068,12 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>166.1</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46261.23945318328</v>
+        <v>46261.24256208582</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
@@ -9176,25 +9087,25 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>PLM_VendorReliability.py</t>
+          <t>pdoc_PLM.xml</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.xml</t>
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45.1</v>
+        <v>3439.1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46261.24255787037</v>
+        <v>46262.48778904308</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>StartFix</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -9204,21 +9115,21 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>PLM-092_StartFix_20260827_054917.md</t>
+          <t>PLM_FindingDefinition.py</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>165.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46261.24256208582</v>
+        <v>46262.48800347281</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
@@ -9232,21 +9143,21 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>pdoc_PLM.xml</t>
+          <t>PLM_AutoEyes.py</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>.xml</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>3439.1</v>
+        <v>225.4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46262.48778904308</v>
+        <v>46262.62534446375</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
@@ -9260,49 +9171,49 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>PLM_FindingDefinition.py</t>
+          <t>PLM_FindingSeverity_Ownership_20260828.md</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>49.4</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46262.48800347281</v>
+        <v>46264.56373508028</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>PLM_AutoEyes.py</t>
+          <t>2026-08-30_13-31-46.snagx</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>225.4</v>
+        <v>179.9</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46262.62534446375</v>
+        <v>46264.57774242717</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
@@ -9311,54 +9222,54 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>GlobalSuppliers</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>PLM_FindingSeverity_Ownership_20260828.md</t>
+          <t>promote_existing_vendor_oes_to_suppliers.py</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.py</t>
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>26.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46264.56373508028</v>
+        <v>46265.34662185683</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Snagit</t>
+          <t>PycharmProjects</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>(root)</t>
+          <t>BigDawgHunt</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30_13-31-46.snagx</t>
+          <t>DeadDawg.xlsx</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>.snagx</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>179.9</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46264.57774242717</v>
+        <v>46265.61821050791</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
@@ -9367,26 +9278,26 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>GlobalSuppliers</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>promote_existing_vendor_oes_to_suppliers.py</t>
+          <t>Deep dive HPS file for Scott 8-1-26.xlsx</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>25</v>
+        <v>9520.6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46265.34662185683</v>
+        <v>46265.62396575566</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
@@ -9395,54 +9306,54 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>BigDawgHunt</t>
+          <t>PLM</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>DeadDawg.xlsx</t>
+          <t>PLM_HPS_vs_EarlyWarning_Comparison_20260828.md</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.md</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>14.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46265.61821050791</v>
+        <v>46265.66668499646</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>PycharmProjects</t>
+          <t>Snagit</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>(root)</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Deep dive HPS file for Scott 8-1-26.xlsx</t>
+          <t>2026-08-31_15-54-00.snagx</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.snagx</t>
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>9520.6</v>
+        <v>378</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46265.62396575566</v>
+        <v>46265.79189159806</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
@@ -9451,104 +9362,20 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>PLM</t>
+          <t>ebayBrowse</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>PLM_HPS_vs_EarlyWarning_Comparison_20260828.md</t>
+          <t>token_file.txt</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>.md</t>
+          <t>.txt</t>
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>46265.64431662859</v>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>PycharmProjects</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>CRPUtils</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>ro_query.sql</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>.sql</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>46265.66668499646</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>Snagit</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>(root)</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31_15-54-00.snagx</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>.snagx</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>46265.79189159806</v>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>PycharmProjects</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>ebayBrowse</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>token_file.txt</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>.txt</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -9564,17 +9391,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9595,25 +9423,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Created</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Modified</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9635,23 +9468,28 @@
           <t>PM Stockout Option Preparation</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>If we are warning of stockouts in a particular category we should also try to find/offer solutions. The Suppliers table in the CRPAF database is a wrangled table organized by OE which can be matched to the OE of our stockout product. Work needs to be done on matching the…</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>46235.40855987269</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="H2" s="3" t="n">
         <v>46235.40995466435</v>
       </c>
-      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9669,25 +9507,30 @@
           <t>CRPUtils is_ready() — support gating on specific tables, not just whole source D</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Problem: CRPUtils/BIWarehouseStatus.isready(requiredsources=[...]) scopes only by source-database prefix (filterbysource matches table.startswith(src+'.'); readiness-view names are BIWarehouse.&lt;Table&gt; (window), space-delimited). So a job is blocked whenever any BIWarehouse…</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>46236.72103969908</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>46236.76986936342</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>46236.76986936342</v>
       </c>
+      <c r="I3" s="3" t="n">
+        <v>46236.76986936342</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -9705,23 +9548,28 @@
           <t>Extend BIWarehouse readiness gating: PMA/BDH orchestrators + close the LostSales</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Follow-up to CRP-010 (which added the top-level BIWarehouse readiness gate to PLMOrchestrator and fixed the CRP-009 requiredtables false-pass in CRPUtils/BIWarehouseStatus.py). Remaining ungated / soft-gated consumers, per the CRP-010 audit doc…</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46237.5136133912</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>46237.5136133912</v>
       </c>
-      <c r="H4" s="2" t="n"/>
+      <c r="H4" s="3" t="n">
+        <v>46237.5136133912</v>
+      </c>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9739,23 +9587,28 @@
           <t>Use the eBay Linear Regression trend signal for new-product hunting (BDH)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>One-line: We already compute a per-item eBay demand/price trend (linear regression over ebayWT) but nothing consumes it — surface the rising-trend items as new-product / stock candidates.over ebayWT) but nothing consumes it — surface the rising-trend items as new-product / stock…</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46237.52962734954</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>46237.52962734954</v>
       </c>
-      <c r="H5" s="2" t="n"/>
+      <c r="H5" s="3" t="n">
+        <v>46237.52962734954</v>
+      </c>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9773,23 +9626,28 @@
           <t>Document BIWarehouse queries for further input</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Over the weekend we committed CRP-009 where we modified the BIWarehouse 'ready' check to allow a subset of the total BIWarehouse list of tables. This allowed a using script to continue even though the full BIWarehouse is not populate. One project we know is hitting this problem…</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="G6" s="3" t="n">
         <v>46237.45476924768</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>46237.53198063657</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>46237.53198052083</v>
       </c>
     </row>
@@ -9809,23 +9667,28 @@
           <t>PLM_Automate</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>We have the green light from PM-A to attempt to automate some of the basic tasks from the PM's that they do not have cycles to ever get to. Leverage what we already did (not sure where) to create emails to suppliers where we need new catalogs. Build pivot tables of suggested MOQ…</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>46247.44281435185</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>46247.44342052083</v>
       </c>
-      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9843,23 +9706,28 @@
           <t>Utility to scrape reports from Sage</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>There are some web based reports in Sage that we should develop a Selenium based utility to download. I know these will be fragile but we don't have this data anywhere else and we should periodically update some data tables. This would be the first one to try:…</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>46252.43921597222</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>46252.43921597222</v>
       </c>
-      <c r="H8" s="2" t="n"/>
+      <c r="H8" s="3" t="n">
+        <v>46252.43921597222</v>
+      </c>
+      <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9877,23 +9745,28 @@
           <t>Early-warning workbook: add All Issues tab (all severities)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>The Component/FinishedGood early-warning workbook action tabs are now filtered to CRITICAL/HIGH only (Supply feedback: stop drowning the urgent signal in green). Add one 'All Issues' tab listing every severity (CRITICAL/HIGH/MEDIUM/LOW), ranked, so the full watch-list stays one…</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>46253.4675408912</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>46253.4675408912</v>
       </c>
-      <c r="H9" s="2" t="n"/>
+      <c r="H9" s="3" t="n">
+        <v>46253.4675408912</v>
+      </c>
+      <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9911,23 +9784,28 @@
           <t>Early warning: surface out-of-stock FGs with open customer orders</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>The early-warning workbook is entirely forecast-driven (predicted stockout from cover vs ETA). It misses the realized case: an FG out of stock NOW with an open customer order/backorder behind it -- a happening-now, dollarized lost sale, arguably a stronger signal than any…</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>46253.4675409375</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>46253.4675409375</v>
       </c>
-      <c r="H10" s="2" t="n"/>
+      <c r="H10" s="3" t="n">
+        <v>46253.4675409375</v>
+      </c>
+      <c r="I10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9945,23 +9823,28 @@
           <t>Redesign PM early-warning email to match Supply's Critical/High spine</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>PM/PM-A early-warning emails currently show green/low items and their 'criticals' do not line up with Supply's. Redesign so all recipients share ONE urgent spine (CRITICAL/HIGH), sliced by role + category: tell each PM what Supply is expediting in their categories, then their…</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>46253.46754097223</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>46253.46754097223</v>
       </c>
-      <c r="H11" s="2" t="n"/>
+      <c r="H11" s="3" t="n">
+        <v>46253.46754097223</v>
+      </c>
+      <c r="I11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9979,23 +9862,28 @@
           <t>Reconcile early-warning workbook counts vs AgentFindings</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>The Supply early-warning workbook (PMAEarlyWarningComponent/FinishedGood, ~1,500 FGs) and the findings table (PMAAgentFindings) are out of sync -- the workbook is populated while the findings emitter shows ~0 active COMPONENTSTOCKOUTRISK and only a handful of CLARITYNONCOVERAGE.…</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>46253.46754100695</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>46253.46754100695</v>
       </c>
-      <c r="H12" s="2" t="n"/>
+      <c r="H12" s="3" t="n">
+        <v>46253.46754100695</v>
+      </c>
+      <c r="I12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -10013,23 +9901,28 @@
           <t>Reconsider strict IWD anchor on early-warning emitters (IWD OR real demand)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>The early-warning emitters (LS04 Pt03/Pt04) were anchored to a valid IWDAnnoucementDate on the finished good. Spot-check of 382 no-IWD PUR goods: 372 genuinely dead (0 sales -- correct to drop) but 8 real sellers (e.g. PENTOSIN ATF 8 20L, ~$28.6K/6mo) that a strict IWD gate…</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>46253.46754105324</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>46253.46754105324</v>
       </c>
-      <c r="H13" s="2" t="n"/>
+      <c r="H13" s="3" t="n">
+        <v>46253.46754105324</v>
+      </c>
+      <c r="I13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -10047,23 +9940,28 @@
           <t>Smell-test coverage for Partium exports (083/084) + confirm fluids scope</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>The Partium exports (PLM083 MysteryShopper/VendorSearch and PLM-084 vendor-discovery outputs) have no standing smell-test contract. Add contracts to PLMSmellTest.py so these shared exports are checked before they go out (Active, Company='CRP', correct division, no IND,…</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>46253.46754108796</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>46253.46754108796</v>
       </c>
-      <c r="H14" s="2" t="n"/>
+      <c r="H14" s="3" t="n">
+        <v>46253.46754108796</v>
+      </c>
+      <c r="I14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -10081,23 +9979,28 @@
           <t>Rename StartFix files to include the PLM Number in play</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Instead of naming these file PLMStartFix20260609194822 replace StartFix with the PLM-xxx number</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="G15" s="3" t="n">
         <v>46253.59937144676</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="H15" s="3" t="n">
         <v>46253.62108938657</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="I15" s="3" t="n">
         <v>46253.62108935185</v>
       </c>
     </row>
@@ -10117,23 +10020,28 @@
           <t>Use Global Supplier results for No Suggestion/Stockout products</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Finding new vendors for 'No Suggestion'/stockout products for non-responsive/non-existant vendors could be accomplished with the data we have (or could request) using the GlobalSuppliers project. To start, we have vendors here: [CRPAF].[dbo].[GlobalSuppliers] and documents we…</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="G16" s="3" t="n">
         <v>46254.62774016204</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>46254.62836875</v>
       </c>
-      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -10151,23 +10059,28 @@
           <t>PLM Overseer — Discovery Agent (Spike)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Goal: An exploratory agent that roams the PLM substrate and reasons from facts to surface candidate patterns no one wrote a query for — the second half of "Automated Eyes" (the eyes that go looking, vs PLM-012 which reports what's already found). Scoped as a spike: the first…</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="G17" s="3" t="n">
         <v>46171.44091947917</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>46255.45345732639</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="I17" s="3" t="n">
         <v>46255.45345729167</v>
       </c>
     </row>
@@ -10187,23 +10100,28 @@
           <t>Import Partium Mystery Shopper Data</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Take the data from Partium (all versions - Mystery Shopper, no suggestion, other data) and evaluate how we pull that into InternetCompData so that we have current competitive retail pricing for our products. Their data is located in this folder: C:\Users\pyearick.CRP\OneDrive -…</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="G18" s="3" t="n">
         <v>46258.36920987268</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="H18" s="3" t="n">
         <v>46258.44464039352</v>
       </c>
-      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -10221,25 +10139,30 @@
           <t>Implement a ro_data.py setup to reduce bash approvals</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Claude ends up doing a lot of data discovery and we run a lot of read-only queries. I end up having to approve all the bash scripts. Claude suggested that for read-only queries that we name them consistenly something like rodata.py and overwrite whatever is there with our…</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>46258.46758680556</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>46258.54739432871</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>46258.54739432871</v>
       </c>
+      <c r="I19" s="3" t="n">
+        <v>46258.54739432871</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -10257,23 +10180,28 @@
           <t>Smell-test the no suggestion, bad vendor, new vendor process</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>PLM-093 added new websites to scrape (AutoMechanika), vendor discovery, document download, OE extraction, analysis, email creation for GlobalSupplier. Did we do it right?? (lol).</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="G20" s="3" t="n">
         <v>46258.66860690972</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>46258.66974016204</v>
       </c>
-      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -10291,23 +10219,28 @@
           <t>Smell-test the no suggestion, bad vendor, new vendor identification process (PLM</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>PLM-093 added new websites to scrape (AutoMechanika), vendor discovery, document download, OE extraction, analysis, email creation for GlobalSupplier. Did we do it right?? (lol).</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="G21" s="3" t="n">
         <v>46258.68702592592</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="H21" s="3" t="n">
         <v>46258.68791446759</v>
       </c>
-      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -10325,23 +10258,28 @@
           <t>Add existing, discovered vendor catalogs to Supplier Listing share folder</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>\\crpfiles\DeptFiles\Automotive R and D\Supplier catalogs and files\2026 Supplier Listings In our AAPEX/AutoMechanika document web scrape we uncovered a number of existing CRP vendors. This makes sense but we should migrate the data for those existing vendors to either the…</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="G22" s="3" t="n">
         <v>46259.76728541667</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="H22" s="3" t="n">
         <v>46259.76990494213</v>
       </c>
-      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -10359,23 +10297,28 @@
           <t>Need all PLM outputs smell test</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>20260826 - Additional embarassment! Please review PLM-081CrossSurfaceConsistencyproposal20260826.md in the PLM folder and let's work on fixing this difficult problem. I feel that we need to have an inventory of every product and look across all of them. We need to somehow look…</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="G23" s="3" t="n">
         <v>46225.79840833334</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="H23" s="3" t="n">
         <v>46260.53686565972</v>
       </c>
-      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -10393,25 +10336,30 @@
           <t xml:space="preserve">Vendor tier: hard chronic-late override so Reliability_Tier can't disagree with </t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Surfaced by PLM-081 Entity Consistency Ledger (and Scott's DEFU call-out, 2026-08-26). PLMVendorReliability.computecompositescore tiers chronically-late vendors as RELIABLE/LOWRISK because MissRatePct=0 dominates and lateness is capped too low — so the reliability TIER…</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="G24" s="3" t="n">
         <v>46261.22263483796</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>46261.24189864584</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>46261.24189864584</v>
       </c>
+      <c r="I24" s="3" t="n">
+        <v>46261.24189864584</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -10429,25 +10377,30 @@
           <t>Fill Rate Diagnostic Meeting</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Our Fill Rate Diagnostic workbook in the SharePoint Results folder C:\Users\pyearick.CRP\OneDrive - CRP Industries Inc\CRPAF\Results is the basis of a pretty important meeting. I don't even remember this workbook but believe the LostSales project creates it. So why am I doing…</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="G25" s="3" t="n">
         <v>46260.34405914352</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>46261.24215644676</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>46261.24215644676</v>
       </c>
+      <c r="I25" s="3" t="n">
+        <v>46261.24215644676</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -10465,25 +10418,30 @@
           <t>Reconcile the meaning of 'critical' across detectors</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>'Critical' uses different dollar bars across detectors: the component/FG cover early-warning uses FGRevenueAtRisk &gt;= $25K (or chargeback &gt;= $5K) + imminent cover; ClarityNonCoverage uses ~$2K annual demand + &lt;30-day cover. Within a detector severity is one consistent function,…</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="G26" s="3" t="n">
         <v>46253.46754112269</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>46262.48228101852</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>46262.48228101852</v>
       </c>
+      <c r="I26" s="3" t="n">
+        <v>46262.48228101852</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -10501,25 +10459,30 @@
           <t>Vendor Reliability Scoring</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>We have a lot of this done already so I think we can pause this for now Origin: LS10 Vendor Summary tab shows fill rate by vendor for a single month. If a vendor is consistently late across multiple products and multiple months, that pattern should be surfaced proactively — even…</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="G27" s="3" t="n">
         <v>46081.55717878472</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>46262.67453498843</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>46262.67453498843</v>
       </c>
+      <c r="I27" s="3" t="n">
+        <v>46262.67453498843</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -10537,28 +10500,33 @@
           <t>StreamLit BDH pages very slow</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Pages where StreamLit is pulling data from BDH, probably this table: FROM [CRPAF].[dbo].[BDH06DataDrivenScoredOpportunities] Are so slow as to be almost unusable. When we select a potential product and hit the radio buttons to filter by eBay, crewAI, etc., the performance is…</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="G28" s="3" t="n">
         <v>46182.29425524305</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="H28" s="3" t="n">
         <v>46262.67509309028</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="I28" s="3" t="n">
         <v>46262.67509305556</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>